--- a/artfynd/A 4856-2025 artfynd.xlsx
+++ b/artfynd/A 4856-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,6 +785,1039 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123191677</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100631</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>627970</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6896489</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123188699</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90963</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>628067</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6896345</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123188795</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79751</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>628049</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6896410</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123190011</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>628044</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6896445</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123189695</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5193</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>628049</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6896410</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123189909</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98399</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>628044</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6896445</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123191668</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90963</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>627970</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6896489</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123191655</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98399</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>627970</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6896489</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123192263</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>627983</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6896429</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4856-2025 artfynd.xlsx
+++ b/artfynd/A 4856-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123191677</v>
+        <v>123191655</v>
       </c>
       <c r="B3" t="n">
-        <v>100631</v>
+        <v>98399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,24 +804,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
@@ -863,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123188699</v>
+        <v>123188795</v>
       </c>
       <c r="B4" t="n">
-        <v>90963</v>
+        <v>79751</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,21 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1205</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628067</v>
+        <v>628049</v>
       </c>
       <c r="R4" t="n">
-        <v>6896345</v>
+        <v>6896410</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -975,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -985,7 +990,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123188795</v>
+        <v>123191668</v>
       </c>
       <c r="B5" t="n">
-        <v>79751</v>
+        <v>90963</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,21 +1033,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628049</v>
+        <v>627970</v>
       </c>
       <c r="R5" t="n">
-        <v>6896410</v>
+        <v>6896489</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1087,7 +1092,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1102,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123190011</v>
+        <v>123189909</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>98399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,31 +1141,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1204,7 +1209,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1214,7 +1219,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123189695</v>
+        <v>123192263</v>
       </c>
       <c r="B7" t="n">
-        <v>5193</v>
+        <v>98365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,31 +1258,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1286,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628049</v>
+        <v>627983</v>
       </c>
       <c r="R7" t="n">
-        <v>6896410</v>
+        <v>6896429</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,7 +1326,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1331,7 +1336,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123189909</v>
+        <v>123191677</v>
       </c>
       <c r="B8" t="n">
-        <v>98399</v>
+        <v>100631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,39 +1379,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219874</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628044</v>
+        <v>627970</v>
       </c>
       <c r="R8" t="n">
-        <v>6896445</v>
+        <v>6896489</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123191668</v>
+        <v>123190011</v>
       </c>
       <c r="B9" t="n">
-        <v>90963</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,38 +1487,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>627970</v>
+        <v>628044</v>
       </c>
       <c r="R9" t="n">
-        <v>6896489</v>
+        <v>6896445</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1550,7 +1555,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1565,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123191655</v>
+        <v>123188699</v>
       </c>
       <c r="B10" t="n">
-        <v>98399</v>
+        <v>90963</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,39 +1608,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219874</v>
+        <v>1205</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>627970</v>
+        <v>628067</v>
       </c>
       <c r="R10" t="n">
-        <v>6896489</v>
+        <v>6896345</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123192263</v>
+        <v>123189695</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>5193</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1716,31 +1716,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>627983</v>
+        <v>628049</v>
       </c>
       <c r="R11" t="n">
-        <v>6896429</v>
+        <v>6896410</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 4856-2025 artfynd.xlsx
+++ b/artfynd/A 4856-2025 artfynd.xlsx
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123188795</v>
+        <v>123191668</v>
       </c>
       <c r="B4" t="n">
-        <v>79751</v>
+        <v>90963</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628049</v>
+        <v>627970</v>
       </c>
       <c r="R4" t="n">
-        <v>6896410</v>
+        <v>6896489</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123191668</v>
+        <v>123188795</v>
       </c>
       <c r="B5" t="n">
-        <v>90963</v>
+        <v>79751</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,21 +1033,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627970</v>
+        <v>628049</v>
       </c>
       <c r="R5" t="n">
-        <v>6896489</v>
+        <v>6896410</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123189909</v>
+        <v>123191677</v>
       </c>
       <c r="B6" t="n">
-        <v>98399</v>
+        <v>100631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,39 +1145,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628044</v>
+        <v>627970</v>
       </c>
       <c r="R6" t="n">
-        <v>6896445</v>
+        <v>6896489</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1209,7 +1204,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1219,7 +1214,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123192263</v>
+        <v>123189909</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>98399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,25 +1253,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1291,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627983</v>
+        <v>628044</v>
       </c>
       <c r="R7" t="n">
-        <v>6896429</v>
+        <v>6896445</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,7 +1321,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1336,7 +1331,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123191677</v>
+        <v>123189695</v>
       </c>
       <c r="B8" t="n">
-        <v>100631</v>
+        <v>5193</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,34 +1374,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627970</v>
+        <v>628049</v>
       </c>
       <c r="R8" t="n">
-        <v>6896489</v>
+        <v>6896410</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1592,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123188699</v>
+        <v>123192263</v>
       </c>
       <c r="B10" t="n">
-        <v>90963</v>
+        <v>98365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,38 +1604,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628067</v>
+        <v>627983</v>
       </c>
       <c r="R10" t="n">
-        <v>6896345</v>
+        <v>6896429</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1667,7 +1672,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1677,7 +1682,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123189695</v>
+        <v>123188699</v>
       </c>
       <c r="B11" t="n">
-        <v>5193</v>
+        <v>90963</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1720,39 +1725,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>1205</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628049</v>
+        <v>628067</v>
       </c>
       <c r="R11" t="n">
-        <v>6896410</v>
+        <v>6896345</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 4856-2025 artfynd.xlsx
+++ b/artfynd/A 4856-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123191655</v>
+        <v>123188699</v>
       </c>
       <c r="B3" t="n">
-        <v>98399</v>
+        <v>90963</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,39 +804,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>627970</v>
+        <v>628067</v>
       </c>
       <c r="R3" t="n">
-        <v>6896489</v>
+        <v>6896345</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123191668</v>
+        <v>123190011</v>
       </c>
       <c r="B4" t="n">
-        <v>90963</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,38 +912,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627970</v>
+        <v>628044</v>
       </c>
       <c r="R4" t="n">
-        <v>6896489</v>
+        <v>6896445</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123188795</v>
+        <v>123189909</v>
       </c>
       <c r="B5" t="n">
-        <v>79751</v>
+        <v>98399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,34 +1033,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628049</v>
+        <v>628044</v>
       </c>
       <c r="R5" t="n">
-        <v>6896410</v>
+        <v>6896445</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1092,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1102,7 +1107,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123191677</v>
+        <v>123188795</v>
       </c>
       <c r="B6" t="n">
-        <v>100631</v>
+        <v>79751</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,21 +1150,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1169,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627970</v>
+        <v>628049</v>
       </c>
       <c r="R6" t="n">
-        <v>6896489</v>
+        <v>6896410</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1204,7 +1209,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1214,7 +1219,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123189909</v>
+        <v>123191668</v>
       </c>
       <c r="B7" t="n">
-        <v>98399</v>
+        <v>90963</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,39 +1262,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219874</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628044</v>
+        <v>627970</v>
       </c>
       <c r="R7" t="n">
-        <v>6896445</v>
+        <v>6896489</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1475,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123190011</v>
+        <v>123191655</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>98399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,31 +1487,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628044</v>
+        <v>627970</v>
       </c>
       <c r="R9" t="n">
-        <v>6896445</v>
+        <v>6896489</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123188699</v>
+        <v>123191677</v>
       </c>
       <c r="B11" t="n">
-        <v>90963</v>
+        <v>100631</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,21 +1725,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1205</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628067</v>
+        <v>627970</v>
       </c>
       <c r="R11" t="n">
-        <v>6896345</v>
+        <v>6896489</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 4856-2025 artfynd.xlsx
+++ b/artfynd/A 4856-2025 artfynd.xlsx
@@ -1475,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123191655</v>
+        <v>123192263</v>
       </c>
       <c r="B9" t="n">
-        <v>98399</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,25 +1487,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>627970</v>
+        <v>627983</v>
       </c>
       <c r="R9" t="n">
-        <v>6896489</v>
+        <v>6896429</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123192263</v>
+        <v>123191655</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>98399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,25 +1604,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>627983</v>
+        <v>627970</v>
       </c>
       <c r="R10" t="n">
-        <v>6896429</v>
+        <v>6896489</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 4856-2025 artfynd.xlsx
+++ b/artfynd/A 4856-2025 artfynd.xlsx
@@ -1475,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123192263</v>
+        <v>123191655</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>98399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,25 +1487,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>627983</v>
+        <v>627970</v>
       </c>
       <c r="R9" t="n">
-        <v>6896429</v>
+        <v>6896489</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123191655</v>
+        <v>123192263</v>
       </c>
       <c r="B10" t="n">
-        <v>98399</v>
+        <v>98365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,25 +1604,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>627970</v>
+        <v>627983</v>
       </c>
       <c r="R10" t="n">
-        <v>6896489</v>
+        <v>6896429</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 4856-2025 artfynd.xlsx
+++ b/artfynd/A 4856-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123188699</v>
+        <v>123190011</v>
       </c>
       <c r="B3" t="n">
-        <v>90963</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,38 +800,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628067</v>
+        <v>628044</v>
       </c>
       <c r="R3" t="n">
-        <v>6896345</v>
+        <v>6896445</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -863,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123190011</v>
+        <v>123189695</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>5193</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,20 +917,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -936,7 +941,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -945,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628044</v>
+        <v>628049</v>
       </c>
       <c r="R4" t="n">
-        <v>6896445</v>
+        <v>6896410</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,7 +1025,7 @@
         <v>123189909</v>
       </c>
       <c r="B5" t="n">
-        <v>98399</v>
+        <v>98402</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1134,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123188795</v>
+        <v>123191655</v>
       </c>
       <c r="B6" t="n">
-        <v>79751</v>
+        <v>98402</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,34 +1155,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628049</v>
+        <v>627970</v>
       </c>
       <c r="R6" t="n">
-        <v>6896410</v>
+        <v>6896489</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1209,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1219,7 +1229,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,7 +1259,7 @@
         <v>123191668</v>
       </c>
       <c r="B7" t="n">
-        <v>90963</v>
+        <v>90966</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1358,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123189695</v>
+        <v>123191677</v>
       </c>
       <c r="B8" t="n">
-        <v>5193</v>
+        <v>100634</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,39 +1384,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628049</v>
+        <v>627970</v>
       </c>
       <c r="R8" t="n">
-        <v>6896410</v>
+        <v>6896489</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,7 +1443,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1448,7 +1453,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123191655</v>
+        <v>123192263</v>
       </c>
       <c r="B9" t="n">
-        <v>98399</v>
+        <v>98368</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,25 +1492,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1520,10 +1525,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>627970</v>
+        <v>627983</v>
       </c>
       <c r="R9" t="n">
-        <v>6896489</v>
+        <v>6896429</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1555,7 +1560,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1565,7 +1570,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123192263</v>
+        <v>123188795</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>79754</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,43 +1609,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>627983</v>
+        <v>628049</v>
       </c>
       <c r="R10" t="n">
-        <v>6896429</v>
+        <v>6896410</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123191677</v>
+        <v>123188699</v>
       </c>
       <c r="B11" t="n">
-        <v>100631</v>
+        <v>90966</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,21 +1725,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>1205</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>627970</v>
+        <v>628067</v>
       </c>
       <c r="R11" t="n">
-        <v>6896489</v>
+        <v>6896345</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 4856-2025 artfynd.xlsx
+++ b/artfynd/A 4856-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123190011</v>
+        <v>123189909</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>98404</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,31 +800,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123189695</v>
+        <v>123191668</v>
       </c>
       <c r="B4" t="n">
-        <v>5193</v>
+        <v>90968</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,39 +921,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628049</v>
+        <v>627970</v>
       </c>
       <c r="R4" t="n">
-        <v>6896410</v>
+        <v>6896489</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -985,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +990,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123189909</v>
+        <v>123190011</v>
       </c>
       <c r="B5" t="n">
-        <v>98402</v>
+        <v>57497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,31 +1029,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1102,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1107,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123191655</v>
+        <v>123189695</v>
       </c>
       <c r="B6" t="n">
-        <v>98402</v>
+        <v>5193</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,27 +1150,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1184,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627970</v>
+        <v>628049</v>
       </c>
       <c r="R6" t="n">
-        <v>6896489</v>
+        <v>6896410</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1219,7 +1214,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,7 +1224,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123191668</v>
+        <v>123191677</v>
       </c>
       <c r="B7" t="n">
-        <v>90966</v>
+        <v>100636</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,21 +1267,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1205</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1368,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123191677</v>
+        <v>123188795</v>
       </c>
       <c r="B8" t="n">
-        <v>100634</v>
+        <v>79756</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,21 +1379,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1408,10 +1403,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627970</v>
+        <v>628049</v>
       </c>
       <c r="R8" t="n">
-        <v>6896489</v>
+        <v>6896410</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1443,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1453,7 +1448,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123192263</v>
+        <v>123191655</v>
       </c>
       <c r="B9" t="n">
-        <v>98368</v>
+        <v>98404</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,25 +1487,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1525,10 +1520,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>627983</v>
+        <v>627970</v>
       </c>
       <c r="R9" t="n">
-        <v>6896429</v>
+        <v>6896489</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1560,7 +1555,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1570,7 +1565,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123188795</v>
+        <v>123188699</v>
       </c>
       <c r="B10" t="n">
-        <v>79754</v>
+        <v>90968</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,21 +1608,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1637,10 +1632,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628049</v>
+        <v>628067</v>
       </c>
       <c r="R10" t="n">
-        <v>6896410</v>
+        <v>6896345</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1672,7 +1667,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1682,7 +1677,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1709,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123188699</v>
+        <v>123192263</v>
       </c>
       <c r="B11" t="n">
-        <v>90966</v>
+        <v>98370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,38 +1716,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628067</v>
+        <v>627983</v>
       </c>
       <c r="R11" t="n">
-        <v>6896345</v>
+        <v>6896429</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 4856-2025 artfynd.xlsx
+++ b/artfynd/A 4856-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123189909</v>
+        <v>123188699</v>
       </c>
       <c r="B3" t="n">
-        <v>98404</v>
+        <v>90974</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,39 +804,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628044</v>
+        <v>628067</v>
       </c>
       <c r="R3" t="n">
-        <v>6896445</v>
+        <v>6896345</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +903,7 @@
         <v>123191668</v>
       </c>
       <c r="B4" t="n">
-        <v>90968</v>
+        <v>90974</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1017,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123190011</v>
+        <v>123191655</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>98410</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,31 +1024,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1062,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628044</v>
+        <v>627970</v>
       </c>
       <c r="R5" t="n">
-        <v>6896445</v>
+        <v>6896489</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1092,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,7 +1102,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123189695</v>
+        <v>123188795</v>
       </c>
       <c r="B6" t="n">
-        <v>5193</v>
+        <v>79757</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,29 +1145,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
@@ -1214,7 +1204,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1224,7 +1214,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123191677</v>
+        <v>123192263</v>
       </c>
       <c r="B7" t="n">
-        <v>100636</v>
+        <v>98376</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,38 +1253,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627970</v>
+        <v>627983</v>
       </c>
       <c r="R7" t="n">
-        <v>6896489</v>
+        <v>6896429</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,7 +1321,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1336,7 +1331,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123188795</v>
+        <v>123190011</v>
       </c>
       <c r="B8" t="n">
-        <v>79756</v>
+        <v>57497</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,38 +1370,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628049</v>
+        <v>628044</v>
       </c>
       <c r="R8" t="n">
-        <v>6896410</v>
+        <v>6896445</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123191655</v>
+        <v>123191677</v>
       </c>
       <c r="B9" t="n">
-        <v>98404</v>
+        <v>100642</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,29 +1491,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219874</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
@@ -1555,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1565,7 +1560,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123188699</v>
+        <v>123189909</v>
       </c>
       <c r="B10" t="n">
-        <v>90968</v>
+        <v>98410</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,34 +1603,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>219874</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628067</v>
+        <v>628044</v>
       </c>
       <c r="R10" t="n">
-        <v>6896345</v>
+        <v>6896445</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123192263</v>
+        <v>123189695</v>
       </c>
       <c r="B11" t="n">
-        <v>98370</v>
+        <v>5193</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1716,31 +1716,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>627983</v>
+        <v>628049</v>
       </c>
       <c r="R11" t="n">
-        <v>6896429</v>
+        <v>6896410</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 4856-2025 artfynd.xlsx
+++ b/artfynd/A 4856-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123188699</v>
+        <v>123188795</v>
       </c>
       <c r="B3" t="n">
-        <v>90974</v>
+        <v>79760</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,21 +804,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628067</v>
+        <v>628049</v>
       </c>
       <c r="R3" t="n">
-        <v>6896345</v>
+        <v>6896410</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -863,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123191668</v>
+        <v>123189695</v>
       </c>
       <c r="B4" t="n">
-        <v>90974</v>
+        <v>5193</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,34 +916,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1205</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627970</v>
+        <v>628049</v>
       </c>
       <c r="R4" t="n">
-        <v>6896489</v>
+        <v>6896410</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -975,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -985,7 +990,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123191655</v>
+        <v>123188699</v>
       </c>
       <c r="B5" t="n">
-        <v>98410</v>
+        <v>90977</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,39 +1033,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627970</v>
+        <v>628067</v>
       </c>
       <c r="R5" t="n">
-        <v>6896489</v>
+        <v>6896345</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123188795</v>
+        <v>123191668</v>
       </c>
       <c r="B6" t="n">
-        <v>79757</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,21 +1145,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628049</v>
+        <v>627970</v>
       </c>
       <c r="R6" t="n">
-        <v>6896410</v>
+        <v>6896489</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123192263</v>
+        <v>123190011</v>
       </c>
       <c r="B7" t="n">
-        <v>98376</v>
+        <v>57497</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,31 +1253,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627983</v>
+        <v>628044</v>
       </c>
       <c r="R7" t="n">
-        <v>6896429</v>
+        <v>6896445</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123190011</v>
+        <v>123192263</v>
       </c>
       <c r="B8" t="n">
-        <v>57497</v>
+        <v>98379</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,31 +1370,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628044</v>
+        <v>627983</v>
       </c>
       <c r="R8" t="n">
-        <v>6896445</v>
+        <v>6896429</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123191677</v>
+        <v>123189909</v>
       </c>
       <c r="B9" t="n">
-        <v>100642</v>
+        <v>98413</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,34 +1491,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>219874</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>627970</v>
+        <v>628044</v>
       </c>
       <c r="R9" t="n">
-        <v>6896489</v>
+        <v>6896445</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1550,7 +1555,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1565,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123189909</v>
+        <v>123191677</v>
       </c>
       <c r="B10" t="n">
-        <v>98410</v>
+        <v>100645</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,39 +1608,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219874</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628044</v>
+        <v>627970</v>
       </c>
       <c r="R10" t="n">
-        <v>6896445</v>
+        <v>6896489</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123189695</v>
+        <v>123191655</v>
       </c>
       <c r="B11" t="n">
-        <v>5193</v>
+        <v>98413</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1720,27 +1720,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>219874</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628049</v>
+        <v>627970</v>
       </c>
       <c r="R11" t="n">
-        <v>6896410</v>
+        <v>6896489</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 4856-2025 artfynd.xlsx
+++ b/artfynd/A 4856-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123188795</v>
+        <v>123188699</v>
       </c>
       <c r="B3" t="n">
-        <v>79760</v>
+        <v>90994</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,21 +804,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628049</v>
+        <v>628067</v>
       </c>
       <c r="R3" t="n">
-        <v>6896410</v>
+        <v>6896345</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -863,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123189695</v>
+        <v>123191668</v>
       </c>
       <c r="B4" t="n">
-        <v>5193</v>
+        <v>90994</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,39 +916,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628049</v>
+        <v>627970</v>
       </c>
       <c r="R4" t="n">
-        <v>6896410</v>
+        <v>6896489</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,7 +975,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,7 +985,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123188699</v>
+        <v>123188795</v>
       </c>
       <c r="B5" t="n">
-        <v>90977</v>
+        <v>79766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,21 +1028,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1057,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628067</v>
+        <v>628049</v>
       </c>
       <c r="R5" t="n">
-        <v>6896345</v>
+        <v>6896410</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1092,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1102,7 +1097,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123191668</v>
+        <v>123189695</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>5194</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,34 +1140,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1205</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627970</v>
+        <v>628049</v>
       </c>
       <c r="R6" t="n">
-        <v>6896489</v>
+        <v>6896410</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123190011</v>
+        <v>123191655</v>
       </c>
       <c r="B7" t="n">
-        <v>57497</v>
+        <v>98430</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,31 +1253,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628044</v>
+        <v>627970</v>
       </c>
       <c r="R7" t="n">
-        <v>6896445</v>
+        <v>6896489</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,7 +1361,7 @@
         <v>123192263</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>123191677</v>
       </c>
       <c r="B9" t="n">
-        <v>100645</v>
+        <v>100662</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123189909</v>
+        <v>123190011</v>
       </c>
       <c r="B10" t="n">
-        <v>98413</v>
+        <v>57503</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1599,31 +1599,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123191655</v>
+        <v>123189909</v>
       </c>
       <c r="B11" t="n">
-        <v>98413</v>
+        <v>98430</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>627970</v>
+        <v>628044</v>
       </c>
       <c r="R11" t="n">
-        <v>6896489</v>
+        <v>6896445</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 4856-2025 artfynd.xlsx
+++ b/artfynd/A 4856-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123188699</v>
+        <v>123192263</v>
       </c>
       <c r="B3" t="n">
-        <v>90994</v>
+        <v>98502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,38 +800,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628067</v>
+        <v>627983</v>
       </c>
       <c r="R3" t="n">
-        <v>6896345</v>
+        <v>6896429</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -863,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +908,7 @@
         <v>123191668</v>
       </c>
       <c r="B4" t="n">
-        <v>90994</v>
+        <v>90999</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1012,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123188795</v>
+        <v>123189695</v>
       </c>
       <c r="B5" t="n">
-        <v>79766</v>
+        <v>5196</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,24 +1033,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
@@ -1087,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1107,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123189695</v>
+        <v>123190011</v>
       </c>
       <c r="B6" t="n">
-        <v>5194</v>
+        <v>57506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,20 +1146,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1160,7 +1170,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1169,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628049</v>
+        <v>628044</v>
       </c>
       <c r="R6" t="n">
-        <v>6896410</v>
+        <v>6896445</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1204,7 +1214,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1214,7 +1224,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123191655</v>
+        <v>123188795</v>
       </c>
       <c r="B7" t="n">
-        <v>98430</v>
+        <v>79771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,39 +1267,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219874</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627970</v>
+        <v>628049</v>
       </c>
       <c r="R7" t="n">
-        <v>6896489</v>
+        <v>6896410</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,7 +1326,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1331,7 +1336,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123192263</v>
+        <v>123191677</v>
       </c>
       <c r="B8" t="n">
-        <v>98396</v>
+        <v>100680</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,43 +1375,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627983</v>
+        <v>627970</v>
       </c>
       <c r="R8" t="n">
-        <v>6896429</v>
+        <v>6896489</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123191677</v>
+        <v>123188699</v>
       </c>
       <c r="B9" t="n">
-        <v>100662</v>
+        <v>90999</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,21 +1491,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1515,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>627970</v>
+        <v>628067</v>
       </c>
       <c r="R9" t="n">
-        <v>6896489</v>
+        <v>6896345</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123190011</v>
+        <v>123191655</v>
       </c>
       <c r="B10" t="n">
-        <v>57503</v>
+        <v>98536</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1599,31 +1599,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628044</v>
+        <v>627970</v>
       </c>
       <c r="R10" t="n">
-        <v>6896445</v>
+        <v>6896489</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,7 +1707,7 @@
         <v>123189909</v>
       </c>
       <c r="B11" t="n">
-        <v>98430</v>
+        <v>98536</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 4856-2025 artfynd.xlsx
+++ b/artfynd/A 4856-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123192263</v>
+        <v>123191655</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>98538</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,25 +800,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>627983</v>
+        <v>627970</v>
       </c>
       <c r="R3" t="n">
-        <v>6896429</v>
+        <v>6896489</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123191668</v>
+        <v>123190011</v>
       </c>
       <c r="B4" t="n">
-        <v>90999</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,38 +917,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627970</v>
+        <v>628044</v>
       </c>
       <c r="R4" t="n">
-        <v>6896489</v>
+        <v>6896445</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123189695</v>
+        <v>123191677</v>
       </c>
       <c r="B5" t="n">
-        <v>5196</v>
+        <v>100682</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,39 +1038,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628049</v>
+        <v>627970</v>
       </c>
       <c r="R5" t="n">
-        <v>6896410</v>
+        <v>6896489</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123190011</v>
+        <v>123189695</v>
       </c>
       <c r="B6" t="n">
-        <v>57506</v>
+        <v>5196</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,20 +1146,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1170,7 +1170,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628044</v>
+        <v>628049</v>
       </c>
       <c r="R6" t="n">
-        <v>6896445</v>
+        <v>6896410</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123188795</v>
+        <v>123189909</v>
       </c>
       <c r="B7" t="n">
-        <v>79771</v>
+        <v>98538</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,34 +1267,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>219874</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628049</v>
+        <v>628044</v>
       </c>
       <c r="R7" t="n">
-        <v>6896410</v>
+        <v>6896445</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1336,7 +1341,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123191677</v>
+        <v>123188699</v>
       </c>
       <c r="B8" t="n">
-        <v>100680</v>
+        <v>91001</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,21 +1384,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1403,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627970</v>
+        <v>628067</v>
       </c>
       <c r="R8" t="n">
-        <v>6896489</v>
+        <v>6896345</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1438,7 +1443,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1448,7 +1453,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123188699</v>
+        <v>123192263</v>
       </c>
       <c r="B9" t="n">
-        <v>90999</v>
+        <v>98504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,38 +1492,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628067</v>
+        <v>627983</v>
       </c>
       <c r="R9" t="n">
-        <v>6896345</v>
+        <v>6896429</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1550,7 +1560,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1570,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123191655</v>
+        <v>123188795</v>
       </c>
       <c r="B10" t="n">
-        <v>98536</v>
+        <v>79773</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,39 +1613,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219874</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>627970</v>
+        <v>628049</v>
       </c>
       <c r="R10" t="n">
-        <v>6896489</v>
+        <v>6896410</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1667,7 +1672,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1677,7 +1682,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123189909</v>
+        <v>123191668</v>
       </c>
       <c r="B11" t="n">
-        <v>98536</v>
+        <v>91001</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1720,39 +1725,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219874</v>
+        <v>1205</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628044</v>
+        <v>627970</v>
       </c>
       <c r="R11" t="n">
-        <v>6896445</v>
+        <v>6896489</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 4856-2025 artfynd.xlsx
+++ b/artfynd/A 4856-2025 artfynd.xlsx
@@ -1251,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123189909</v>
+        <v>123188699</v>
       </c>
       <c r="B7" t="n">
-        <v>98538</v>
+        <v>91001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,39 +1267,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219874</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628044</v>
+        <v>628067</v>
       </c>
       <c r="R7" t="n">
-        <v>6896445</v>
+        <v>6896345</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1331,7 +1326,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,7 +1336,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123188699</v>
+        <v>123189909</v>
       </c>
       <c r="B8" t="n">
-        <v>91001</v>
+        <v>98538</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,34 +1379,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>219874</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628067</v>
+        <v>628044</v>
       </c>
       <c r="R8" t="n">
-        <v>6896345</v>
+        <v>6896445</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 4856-2025 artfynd.xlsx
+++ b/artfynd/A 4856-2025 artfynd.xlsx
@@ -1251,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123188699</v>
+        <v>123189909</v>
       </c>
       <c r="B7" t="n">
-        <v>91001</v>
+        <v>98538</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,34 +1267,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1205</v>
+        <v>219874</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628067</v>
+        <v>628044</v>
       </c>
       <c r="R7" t="n">
-        <v>6896345</v>
+        <v>6896445</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1336,7 +1341,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123189909</v>
+        <v>123188699</v>
       </c>
       <c r="B8" t="n">
-        <v>98538</v>
+        <v>91001</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,39 +1384,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219874</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628044</v>
+        <v>628067</v>
       </c>
       <c r="R8" t="n">
-        <v>6896445</v>
+        <v>6896345</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 4856-2025 artfynd.xlsx
+++ b/artfynd/A 4856-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123191655</v>
+        <v>123192263</v>
       </c>
       <c r="B3" t="n">
-        <v>98538</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,25 +800,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>627970</v>
+        <v>627983</v>
       </c>
       <c r="R3" t="n">
-        <v>6896489</v>
+        <v>6896429</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1025,7 +1025,7 @@
         <v>123191677</v>
       </c>
       <c r="B5" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123189695</v>
+        <v>123188795</v>
       </c>
       <c r="B6" t="n">
-        <v>5196</v>
+        <v>79773</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,29 +1150,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
@@ -1214,7 +1209,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1224,7 +1219,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123189909</v>
+        <v>123191668</v>
       </c>
       <c r="B7" t="n">
-        <v>98538</v>
+        <v>91001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,39 +1262,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219874</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628044</v>
+        <v>627970</v>
       </c>
       <c r="R7" t="n">
-        <v>6896445</v>
+        <v>6896489</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1331,7 +1321,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,7 +1331,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1480,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123192263</v>
+        <v>123191655</v>
       </c>
       <c r="B9" t="n">
-        <v>98504</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,25 +1482,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1525,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>627983</v>
+        <v>627970</v>
       </c>
       <c r="R9" t="n">
-        <v>6896429</v>
+        <v>6896489</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1560,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1570,7 +1560,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123188795</v>
+        <v>123189909</v>
       </c>
       <c r="B10" t="n">
-        <v>79773</v>
+        <v>98113</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,34 +1603,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>219874</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628049</v>
+        <v>628044</v>
       </c>
       <c r="R10" t="n">
-        <v>6896410</v>
+        <v>6896445</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1672,7 +1667,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1682,7 +1677,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1709,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123191668</v>
+        <v>123189695</v>
       </c>
       <c r="B11" t="n">
-        <v>91001</v>
+        <v>5196</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,34 +1720,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1205</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>627970</v>
+        <v>628049</v>
       </c>
       <c r="R11" t="n">
-        <v>6896489</v>
+        <v>6896410</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 4856-2025 artfynd.xlsx
+++ b/artfynd/A 4856-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108929265</v>
+        <v>123188699</v>
       </c>
       <c r="B2" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Mpd</t>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>627985.0750849419</v>
+        <v>628067</v>
       </c>
       <c r="R2" t="n">
-        <v>6896351.878040161</v>
+        <v>6896345</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,67 +770,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123192263</v>
+        <v>123191668</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>627983</v>
+        <v>627970</v>
       </c>
       <c r="R3" t="n">
-        <v>6896429</v>
+        <v>6896489</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,55 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123190011</v>
+        <v>123188795</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628044</v>
+        <v>628049</v>
       </c>
       <c r="R4" t="n">
-        <v>6896445</v>
+        <v>6896410</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -985,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123191677</v>
+        <v>123190011</v>
       </c>
       <c r="B5" t="n">
-        <v>100257</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627970</v>
+        <v>628044</v>
       </c>
       <c r="R5" t="n">
-        <v>6896489</v>
+        <v>6896445</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,15 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123188795</v>
+        <v>108928678</v>
       </c>
       <c r="B6" t="n">
-        <v>79773</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57825</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,37 +1119,47 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>100096</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+          <t>Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628049</v>
+        <v>628065</v>
       </c>
       <c r="R6" t="n">
-        <v>6896410</v>
+        <v>6896404</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1204,22 +1183,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,27 +1213,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123191668</v>
+        <v>123189695</v>
       </c>
       <c r="B7" t="n">
-        <v>91001</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,34 +1236,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1205</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627970</v>
+        <v>628049</v>
       </c>
       <c r="R7" t="n">
-        <v>6896489</v>
+        <v>6896410</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1331,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,15 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123188699</v>
+        <v>123189909</v>
       </c>
       <c r="B8" t="n">
-        <v>91001</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,34 +1348,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>219874</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628067</v>
+        <v>628044</v>
       </c>
       <c r="R8" t="n">
-        <v>6896345</v>
+        <v>6896445</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1433,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1443,7 +1422,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,12 +1452,7 @@
         <v>123191655</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,37 +1561,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123189909</v>
+        <v>123192263</v>
       </c>
       <c r="B10" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1632,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628044</v>
+        <v>627983</v>
       </c>
       <c r="R10" t="n">
-        <v>6896445</v>
+        <v>6896429</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1667,7 +1636,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1677,7 +1646,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,15 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123189695</v>
+        <v>108929265</v>
       </c>
       <c r="B11" t="n">
-        <v>5196</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,42 +1684,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+          <t>Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628049</v>
+        <v>627985</v>
       </c>
       <c r="R11" t="n">
-        <v>6896410</v>
+        <v>6896352</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1779,22 +1739,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,15 +1769,230 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123191705</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>627985</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6896569</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Flera kvadratmeter</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123191677</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>627970</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6896489</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4856-2025 artfynd.xlsx
+++ b/artfynd/A 4856-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123191668</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123191655</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123191677</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123188699</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123188795</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123190011</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108928678</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1553,6 +1593,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123189695</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1665,6 +1710,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123189909</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1777,6 +1827,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123192263</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1885,6 +1940,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108929265</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1993,8 +2053,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123191705</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>